--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:05:33+00:00</t>
+    <t>2023-05-08T14:07:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:07:06+00:00</t>
+    <t>2023-05-08T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:23:05+00:00</t>
+    <t>2023-05-08T14:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T14:48:00+00:00</t>
+    <t>2023-05-08T15:19:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:19:54+00:00</t>
+    <t>2023-05-08T15:31:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T15:31:47+00:00</t>
+    <t>2023-05-08T16:10:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T16:10:55+00:00</t>
+    <t>2023-05-08T18:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:38:59+00:00</t>
+    <t>2023-05-08T18:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T18:49:00+00:00</t>
+    <t>2023-05-08T19:06:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:06:08+00:00</t>
+    <t>2023-05-08T19:17:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:17:16+00:00</t>
+    <t>2023-05-08T19:36:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:36:32+00:00</t>
+    <t>2023-05-08T19:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:37:24+00:00</t>
+    <t>2023-05-08T19:39:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:39:41+00:00</t>
+    <t>2023-05-08T19:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:40:43+00:00</t>
+    <t>2023-05-08T19:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:42:22+00:00</t>
+    <t>2023-05-08T19:53:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T19:53:59+00:00</t>
+    <t>2023-05-08T21:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:00:30+00:00</t>
+    <t>2023-05-08T21:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:01:17+00:00</t>
+    <t>2023-05-09T15:00:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>4.3.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,6 +293,9 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
+    <t>clinical.diagnostics</t>
+  </si>
+  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -376,7 +379,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -434,6 +437,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -484,6 +491,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -501,7 +512,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -581,7 +592,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -614,7 +625,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -706,68 +717,68 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.code.text</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.text</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -795,7 +806,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
 </t>
   </si>
   <si>
@@ -836,7 +847,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -894,7 +905,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -938,7 +949,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -991,7 +1002,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1135,13 +1146,13 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
+    <t>SNOMED CT Body site concepts</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1261,7 +1272,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1427,7 +1438,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1449,7 +1460,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1464,10 +1475,14 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1517,7 +1532,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2156,7 +2171,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2164,10 +2179,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2178,7 +2193,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>82</v>
@@ -2187,19 +2202,19 @@
         <v>82</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2249,13 +2264,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2284,10 +2299,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2298,7 +2313,7 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>82</v>
@@ -2307,16 +2322,16 @@
         <v>82</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2367,19 +2382,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2402,10 +2417,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2416,28 +2431,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2487,19 +2502,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2522,10 +2537,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2536,7 +2551,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2548,16 +2563,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2583,13 +2598,13 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>82</v>
@@ -2607,19 +2622,19 @@
         <v>82</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2642,21 +2657,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2668,16 +2683,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2727,19 +2742,19 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>82</v>
@@ -2751,7 +2766,7 @@
         <v>82</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2762,14 +2777,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2788,16 +2803,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2847,7 +2862,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2859,7 +2874,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2871,7 +2886,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2882,10 +2897,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2908,13 +2923,13 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2953,17 +2968,17 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2975,7 +2990,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -2998,13 +3013,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>82</v>
@@ -3014,10 +3029,10 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>82</v>
@@ -3026,13 +3041,13 @@
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3083,7 +3098,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3092,10 +3107,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3118,14 +3133,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3138,25 +3153,25 @@
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3205,7 +3220,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3217,7 +3232,7 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3229,7 +3244,7 @@
         <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>82</v>
@@ -3240,10 +3255,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3263,20 +3278,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3325,7 +3340,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3337,22 +3352,22 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3360,14 +3375,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3383,20 +3398,20 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3445,7 +3460,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3457,19 +3472,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3480,14 +3495,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3503,19 +3518,19 @@
         <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3565,7 +3580,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3577,19 +3592,19 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -3600,10 +3615,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3611,34 +3626,34 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3663,13 +3678,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -3687,34 +3702,34 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3722,10 +3737,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3748,19 +3763,19 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3785,13 +3800,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3809,7 +3824,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3821,7 +3836,7 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -3833,10 +3848,10 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -3844,21 +3859,21 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>82</v>
@@ -3867,22 +3882,22 @@
         <v>82</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3907,11 +3922,11 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -3929,45 +3944,45 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3978,7 +3993,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -3990,13 +4005,13 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4047,13 +4062,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -4071,7 +4086,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4082,14 +4097,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4108,16 +4123,16 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4155,19 +4170,19 @@
         <v>82</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4179,7 +4194,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4191,7 +4206,7 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4202,10 +4217,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4225,22 +4240,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4289,7 +4304,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4301,7 +4316,7 @@
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4310,10 +4325,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4324,10 +4339,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4338,7 +4353,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4347,22 +4362,22 @@
         <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4372,7 +4387,7 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>82</v>
@@ -4411,19 +4426,19 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -4432,10 +4447,10 @@
         <v>82</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4446,10 +4461,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4457,10 +4472,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
@@ -4469,22 +4484,22 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4533,34 +4548,34 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4568,10 +4583,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4591,19 +4606,19 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4653,7 +4668,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4665,7 +4680,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4674,13 +4689,13 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4688,21 +4703,21 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>82</v>
@@ -4711,22 +4726,22 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4775,34 +4790,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4810,21 +4825,21 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -4833,22 +4848,22 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4885,44 +4900,44 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4930,23 +4945,23 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>82</v>
@@ -4955,22 +4970,22 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5019,34 +5034,34 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5054,10 +5069,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5068,7 +5083,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>82</v>
@@ -5077,19 +5092,19 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5139,19 +5154,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5160,13 +5175,13 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5174,10 +5189,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5185,7 +5200,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>81</v>
@@ -5197,20 +5212,20 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5259,7 +5274,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5271,22 +5286,22 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5294,10 +5309,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5305,10 +5320,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5317,22 +5332,22 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5369,68 +5384,68 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5439,22 +5454,22 @@
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5503,45 +5518,45 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5552,7 +5567,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5564,19 +5579,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5601,13 +5616,13 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5625,19 +5640,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -5646,10 +5661,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5660,21 +5675,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5686,19 +5701,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5723,11 +5738,11 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5745,7 +5760,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5757,33 +5772,33 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5794,7 +5809,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5806,13 +5821,13 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>221</v>
+        <v>95</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5863,13 +5878,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -5887,7 +5902,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5898,14 +5913,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5924,16 +5939,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5971,19 +5986,19 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5995,7 +6010,7 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6007,7 +6022,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6018,10 +6033,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6041,22 +6056,22 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6105,7 +6120,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6117,7 +6132,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6126,10 +6141,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6140,10 +6155,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6154,7 +6169,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>82</v>
@@ -6163,22 +6178,22 @@
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6188,7 +6203,7 @@
         <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>82</v>
@@ -6227,19 +6242,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6248,10 +6263,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6262,10 +6277,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6279,7 +6294,7 @@
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6288,19 +6303,19 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6349,7 +6364,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6361,7 +6376,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6370,10 +6385,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6384,10 +6399,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6398,7 +6413,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6410,16 +6425,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6445,13 +6460,13 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>82</v>
@@ -6469,45 +6484,45 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6518,7 +6533,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6530,19 +6545,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6567,13 +6582,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6591,19 +6606,19 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6612,10 +6627,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6626,10 +6641,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6640,7 +6655,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6652,16 +6667,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6711,45 +6726,45 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6760,7 +6775,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6772,16 +6787,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6831,45 +6846,45 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6892,19 +6907,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6953,7 +6968,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6965,7 +6980,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -6974,10 +6989,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6988,10 +7003,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7002,7 +7017,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7014,13 +7029,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7071,13 +7086,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7095,7 +7110,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7106,14 +7121,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7132,16 +7147,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7191,7 +7206,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7203,7 +7218,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7215,7 +7230,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7226,14 +7241,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7246,25 +7261,25 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7313,7 +7328,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7325,7 +7340,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7337,7 +7352,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7348,10 +7363,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7362,7 +7377,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7374,13 +7389,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7431,19 +7446,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7452,10 +7467,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7466,10 +7481,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7480,7 +7495,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7492,13 +7507,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7549,19 +7564,19 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI47" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>413</v>
-      </c>
       <c r="AJ47" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7570,10 +7585,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7584,10 +7599,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7598,7 +7613,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7610,19 +7625,19 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7647,13 +7662,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7671,31 +7686,31 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7706,10 +7721,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7732,19 +7747,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7769,13 +7784,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7793,7 +7808,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7805,19 +7820,19 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7828,10 +7843,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7842,7 +7857,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7854,17 +7869,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7913,19 +7928,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7937,7 +7952,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7948,10 +7963,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7962,7 +7977,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -7974,13 +7989,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8031,19 +8046,19 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8052,10 +8067,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8066,10 +8081,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8089,19 +8104,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8151,7 +8166,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8163,7 +8178,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8172,10 +8187,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8186,10 +8201,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8209,19 +8224,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8271,7 +8286,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8283,7 +8298,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8292,10 +8307,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8306,10 +8321,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8329,22 +8344,22 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8393,7 +8408,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8405,7 +8420,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>104</v>
+        <v>467</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8414,10 +8429,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8428,10 +8443,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8442,7 +8457,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8454,13 +8469,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8511,13 +8526,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8535,7 +8550,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8546,14 +8561,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8572,16 +8587,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8631,7 +8646,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8643,7 +8658,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8655,7 +8670,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8666,14 +8681,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8686,25 +8701,25 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8753,7 +8768,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8765,7 +8780,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -8777,7 +8792,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8788,10 +8803,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8799,10 +8814,10 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -8811,22 +8826,22 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8851,58 +8866,58 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Y58" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF58" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="Z58" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>469</v>
-      </c>
       <c r="AG58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8910,10 +8925,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8924,7 +8939,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -8933,22 +8948,22 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -8997,45 +9012,45 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9046,7 +9061,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9058,19 +9073,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9095,13 +9110,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9119,19 +9134,19 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9140,10 +9155,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9154,14 +9169,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9180,19 +9195,19 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9217,13 +9232,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9241,7 +9256,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9253,33 +9268,33 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9305,16 +9320,16 @@
         <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9363,7 +9378,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9375,7 +9390,7 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9384,10 +9399,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:00:51+00:00</t>
+    <t>2023-05-09T15:03:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2414" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:03:02+00:00</t>
+    <t>2023-05-09T15:34:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.3.0</t>
+    <t>4.0.1</t>
   </si>
   <si>
     <t>Kind</t>
@@ -293,9 +293,6 @@
     <t>Observation[classCode=OBS, moodCode=EVN]</t>
   </si>
   <si>
-    <t>clinical.diagnostics</t>
-  </si>
-  <si>
     <t>Observation.id</t>
   </si>
   <si>
@@ -379,7 +376,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -437,10 +434,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -491,10 +484,6 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -512,7 +501,7 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -592,7 +581,7 @@
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
   </si>
   <si>
-    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
+    <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
   </si>
   <si>
     <t>Event.partOf</t>
@@ -625,7 +614,7 @@
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-status|4.3.0</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -717,6 +706,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
     <t>Unique id for inter-element referencing</t>
   </si>
   <si>
@@ -775,10 +768,6 @@
     <t>Observation.code.text</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
     <t>Plain text representation of the concept</t>
   </si>
   <si>
@@ -806,7 +795,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location|Organization|Procedure|Practitioner|Medication|Substance)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -847,7 +836,7 @@
     <t>The actual focus of an observation when it is not the patient of record representing something or someone associated with the patient such as a spouse, parent, fetus, or donor. For example, fetus observations in a mother's record.  The focus of an observation could also be an existing condition,  an intervention, the subject's diet,  another observation of the subject,  or a body structure such as tumor or implanted device.   An example use case would be using the Observation resource to capture whether the mother is trained to change her child's tracheostomy tube. In this example, the child is the patient of record and the mother is the focus.</t>
   </si>
   <si>
-    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4B/extension-observation-focuscode.html).</t>
+    <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -905,7 +894,7 @@
     <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
   </si>
   <si>
-    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4B/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
+    <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
   </si>
   <si>
     <t>Knowing when an observation was deemed true is important to its relevance as well as determining trends.</t>
@@ -949,7 +938,7 @@
     <t>The date and time this version of the observation was made available to providers, typically after the results have been reviewed and verified.</t>
   </si>
   <si>
-    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4B/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
+    <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
@@ -1002,7 +991,7 @@
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1146,13 +1135,13 @@
   </si>
   <si>
     <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4B/extension-bodysite.html).</t>
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
     <t>example</t>
   </si>
   <si>
-    <t>SNOMED CT Body site concepts</t>
+    <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
@@ -1272,7 +1261,7 @@
     <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -1438,7 +1427,7 @@
     <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
   </si>
   <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4B/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
   </si>
   <si>
     <t>Relationships established by OBX-4 usage</t>
@@ -1460,7 +1449,7 @@
     <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
   </si>
   <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4B/observation.html#obsgrouping) below.</t>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
   </si>
   <si>
     <t>.targetObservation</t>
@@ -1475,14 +1464,10 @@
     <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
   </si>
   <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
@@ -1532,7 +1517,7 @@
     <t>Actual component result</t>
   </si>
   <si>
-    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4B/observation.html#notes) below.</t>
+    <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
   </si>
   <si>
     <t>363714003 |Interprets| &lt; 441742003 |Evaluation finding|</t>
@@ -2171,7 +2156,7 @@
         <v>90</v>
       </c>
       <c r="AO2" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>82</v>
@@ -2179,10 +2164,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2193,28 +2178,28 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J3" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J3" t="s" s="2">
+      <c r="K3" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="M3" t="s" s="2">
+      <c r="N3" t="s" s="2">
         <v>97</v>
-      </c>
-      <c r="N3" t="s" s="2">
-        <v>98</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2264,13 +2249,13 @@
         <v>82</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>82</v>
@@ -2299,10 +2284,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2313,25 +2298,25 @@
         <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J4" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K4" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M4" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2382,19 +2367,19 @@
         <v>82</v>
       </c>
       <c r="AF4" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AG4" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>82</v>
@@ -2417,10 +2402,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2431,28 +2416,28 @@
         <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I5" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H5" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I5" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="J5" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2502,19 +2487,19 @@
         <v>82</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>82</v>
@@ -2537,10 +2522,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2551,7 +2536,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>82</v>
@@ -2563,16 +2548,16 @@
         <v>82</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="M6" t="s" s="2">
+      <c r="N6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2598,43 +2583,43 @@
         <v>82</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="Y6" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Z6" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>120</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>82</v>
@@ -2657,21 +2642,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>82</v>
@@ -2683,16 +2668,16 @@
         <v>82</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2742,31 +2727,31 @@
         <v>82</v>
       </c>
       <c r="AF7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="AG7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ7" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>82</v>
@@ -2777,14 +2762,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2803,16 +2788,16 @@
         <v>82</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>133</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>134</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2862,7 +2847,7 @@
         <v>82</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2874,7 +2859,7 @@
         <v>82</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>82</v>
@@ -2886,7 +2871,7 @@
         <v>82</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>82</v>
@@ -2897,10 +2882,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2923,13 +2908,13 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>139</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2968,17 +2953,17 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2990,7 +2975,7 @@
         <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>82</v>
@@ -3013,13 +2998,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>82</v>
@@ -3029,11 +3014,11 @@
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H10" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H10" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="I10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3041,13 +3026,13 @@
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3098,7 +3083,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3107,10 +3092,10 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>82</v>
@@ -3133,14 +3118,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3153,25 +3138,25 @@
         <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="O11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>82</v>
@@ -3220,7 +3205,7 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -3232,7 +3217,7 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>82</v>
@@ -3244,7 +3229,7 @@
         <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>82</v>
@@ -3255,10 +3240,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3278,20 +3263,20 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>82</v>
@@ -3340,7 +3325,7 @@
         <v>82</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3352,22 +3337,22 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AO12" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AP12" t="s" s="2">
         <v>82</v>
@@ -3375,14 +3360,14 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -3398,20 +3383,20 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3460,7 +3445,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3472,19 +3457,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3495,14 +3480,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3518,19 +3503,19 @@
         <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>180</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3580,7 +3565,7 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3592,19 +3577,19 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>82</v>
@@ -3615,10 +3600,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3626,34 +3611,34 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G15" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I15" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G15" t="s" s="2">
+      <c r="J15" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I15" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J15" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>191</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -3678,58 +3663,58 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="Z15" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>192</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AM15" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AO15" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>199</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -3737,10 +3722,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3763,19 +3748,19 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -3800,13 +3785,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -3824,7 +3809,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3836,7 +3821,7 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -3848,10 +3833,10 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -3859,45 +3844,45 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J17" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J17" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="O17" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
@@ -3922,67 +3907,67 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF17" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AG17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AH17" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI17" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ17" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK17" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AA17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AG17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH17" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ17" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AP17" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>222</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3993,7 +3978,7 @@
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4005,13 +3990,13 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4062,13 +4047,13 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>82</v>
@@ -4086,7 +4071,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4097,14 +4082,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4123,16 +4108,16 @@
         <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4170,19 +4155,19 @@
         <v>82</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4194,7 +4179,7 @@
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4206,7 +4191,7 @@
         <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4217,10 +4202,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4240,22 +4225,22 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="O20" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>82</v>
@@ -4304,7 +4289,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4316,7 +4301,7 @@
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4325,10 +4310,10 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4339,10 +4324,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4353,31 +4338,31 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J21" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K21" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>82</v>
@@ -4387,70 +4372,70 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="AG21" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4461,10 +4446,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4472,34 +4457,34 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G22" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J22" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K22" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -4548,34 +4533,34 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM22" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -4583,10 +4568,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4606,19 +4591,19 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4668,7 +4653,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4680,7 +4665,7 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4689,13 +4674,13 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -4703,45 +4688,45 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J24" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G24" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4790,34 +4775,34 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM24" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="AN24" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -4825,45 +4810,45 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K25" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -4900,44 +4885,44 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AF25" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="AG25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AL25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
@@ -4945,47 +4930,47 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J26" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G26" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J26" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K26" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5034,34 +5019,34 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
@@ -5069,10 +5054,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5083,28 +5068,28 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K27" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>298</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5154,19 +5139,19 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>82</v>
@@ -5175,13 +5160,13 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
@@ -5189,10 +5174,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5200,7 +5185,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>81</v>
@@ -5212,20 +5197,20 @@
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5274,7 +5259,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5286,22 +5271,22 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5309,10 +5294,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5320,34 +5305,34 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J29" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G29" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J29" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K29" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5384,92 +5369,92 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI29" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP29" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J30" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J30" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K30" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5518,45 +5503,45 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5567,7 +5552,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>82</v>
@@ -5579,19 +5564,19 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O31" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5616,55 +5601,55 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI31" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Y31" t="s" s="2">
+      <c r="AJ31" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AG31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH31" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI31" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -5675,21 +5660,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -5701,19 +5686,19 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5738,11 +5723,11 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Y32" s="2"/>
       <c r="Z32" t="s" s="2">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5760,7 +5745,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5772,33 +5757,33 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5809,7 +5794,7 @@
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -5821,13 +5806,13 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5878,13 +5863,13 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
@@ -5902,7 +5887,7 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -5913,14 +5898,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5939,16 +5924,16 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5986,19 +5971,19 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6010,7 +5995,7 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6022,7 +6007,7 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6033,10 +6018,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6056,22 +6041,22 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6120,7 +6105,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6132,7 +6117,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6141,10 +6126,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6155,10 +6140,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6169,31 +6154,31 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J36" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K36" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
@@ -6203,7 +6188,7 @@
         <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>82</v>
@@ -6242,19 +6227,19 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>82</v>
@@ -6263,10 +6248,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6277,10 +6262,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6294,7 +6279,7 @@
         <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6303,19 +6288,19 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6364,7 +6349,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6376,7 +6361,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6385,10 +6370,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6399,10 +6384,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6413,7 +6398,7 @@
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6425,16 +6410,16 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6460,69 +6445,69 @@
         <v>82</v>
       </c>
       <c r="X38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="Y38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AA38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AG38" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH38" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ38" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>368</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6533,7 +6518,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6545,19 +6530,19 @@
         <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6582,55 +6567,55 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6641,10 +6626,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6655,7 +6640,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6667,16 +6652,16 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6726,45 +6711,45 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>386</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6775,7 +6760,7 @@
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6787,16 +6772,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6846,45 +6831,45 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP41" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>395</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6907,19 +6892,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -6968,7 +6953,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6980,7 +6965,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -6989,10 +6974,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7003,10 +6988,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7017,7 +7002,7 @@
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7029,13 +7014,13 @@
         <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7086,13 +7071,13 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>82</v>
@@ -7110,7 +7095,7 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7121,14 +7106,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7147,16 +7132,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7206,7 +7191,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7218,7 +7203,7 @@
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7230,7 +7215,7 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7241,14 +7226,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7261,25 +7246,25 @@
         <v>82</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7328,7 +7313,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7340,7 +7325,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7352,7 +7337,7 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7363,10 +7348,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7377,7 +7362,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7389,13 +7374,13 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7446,19 +7431,19 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7467,10 +7452,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7481,10 +7466,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7495,7 +7480,7 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -7507,13 +7492,13 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7564,31 +7549,31 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7599,10 +7584,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7613,7 +7598,7 @@
         <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>82</v>
@@ -7625,19 +7610,19 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7662,55 +7647,55 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AM48" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AA48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF48" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AG48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH48" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ48" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AN48" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -7721,10 +7706,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7747,19 +7732,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -7784,13 +7769,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -7808,7 +7793,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7820,19 +7805,19 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -7843,10 +7828,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7857,7 +7842,7 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -7869,17 +7854,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -7928,19 +7913,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -7952,7 +7937,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -7963,10 +7948,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7977,7 +7962,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>82</v>
@@ -7989,13 +7974,13 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8046,31 +8031,31 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8081,10 +8066,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8104,19 +8089,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8166,7 +8151,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8178,7 +8163,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8187,10 +8172,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8201,10 +8186,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8224,19 +8209,19 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N53" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8286,7 +8271,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8298,7 +8283,7 @@
         <v>82</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>82</v>
@@ -8307,10 +8292,10 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8321,10 +8306,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8344,22 +8329,22 @@
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="O54" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8408,7 +8393,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8420,7 +8405,7 @@
         <v>82</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>467</v>
+        <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8429,10 +8414,10 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8443,10 +8428,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8457,7 +8442,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8469,13 +8454,13 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8526,13 +8511,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -8550,7 +8535,7 @@
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8561,14 +8546,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8587,16 +8572,16 @@
         <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8646,7 +8631,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8658,7 +8643,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8670,7 +8655,7 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -8681,14 +8666,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8701,25 +8686,25 @@
         <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8768,7 +8753,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8780,7 +8765,7 @@
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -8792,7 +8777,7 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -8803,10 +8788,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8814,34 +8799,34 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J58" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K58" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -8866,13 +8851,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -8890,34 +8875,34 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -8925,10 +8910,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8939,31 +8924,31 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J59" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="H59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>94</v>
-      </c>
       <c r="K59" t="s" s="2">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9012,45 +8997,45 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>484</v>
-      </c>
       <c r="AM59" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9061,7 +9046,7 @@
         <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>82</v>
@@ -9073,19 +9058,19 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9110,55 +9095,55 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AI60" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="Y60" t="s" s="2">
+      <c r="AJ60" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="AN60" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9169,14 +9154,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9195,19 +9180,19 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O61" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9232,13 +9217,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9256,7 +9241,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9268,33 +9253,33 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9320,16 +9305,16 @@
         <v>83</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9378,7 +9363,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9390,7 +9375,7 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9399,10 +9384,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>

--- a/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
+++ b/branches/Richard/StructureDefinition-viral-load-test-result.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-09T15:34:42+00:00</t>
+    <t>2023-05-09T15:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
